--- a/outline/outline.xlsx
+++ b/outline/outline.xlsx
@@ -713,7 +713,7 @@
   The hook isn't his situation. It's the gap between what he's doing and what he should be doing. The reader recognizes that   
   person.                                                    
 He hears banging throughout the simulation. It's his wife at his office door. Oh shit he's late, drops out to go home. He missed dinner, kids are running around, wife is overwhelmed. It's already bedtime.
-Ramona is pregnant with 3rd (taboo). She wants him present for this phase. Sam's choice: legacy vs. presence. NOT money — they're set. The job is pure ego.</t>
+Ramona is pregnant with 3rd (taboo). She wants him present for this phase. Sam's choice: legacy vs. presence. NOT money — they're set.</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -803,9 +803,9 @@
         <is>
           <t>Ramona at museum, Sam "planning a trip" but actually hunting contracts. Glenn appears with colonization  
     offer. Sam gets excited, rationalizes. Ramona comes home, supportive but sees through him. Gets to her real opinion        
-    eventually. He chooses ego.  
+    eventually.  
 Bored as fuck. Planning a trip with his AI. Checks inbox and takes the call. It's the physical manifestation of Glenn. Colonization project. Genetic seed ship. His name on every planet. The ultimate legacy. Gets a briefing without a ton of other info
-Ramona is pregnant with 3rd (taboo). She wants him present for this phase. Sam's choice: legacy vs. presence. NOT money — they're set. The job is pure ego.</t>
+Ramona is pregnant with 3rd (taboo). She wants him present for this phase. Sam's choice: legacy vs. presence. NOT money — they're set.</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
